--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484838_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484838_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1776</v>
+        <v>3.9273</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3277</v>
+        <v>3.289</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8499</v>
+        <v>0.6383</v>
       </c>
       <c r="G2" t="n">
         <v>2.1081</v>
@@ -610,13 +610,13 @@
         <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8242</v>
+        <v>0.5739</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0276</v>
+        <v>-0.0111</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7966</v>
+        <v>0.585</v>
       </c>
       <c r="V2" t="n">
         <v>0.3018</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4957</v>
+        <v>1.6726</v>
       </c>
       <c r="E3" t="n">
-        <v>3.628</v>
+        <v>3.1223</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1322</v>
+        <v>-1.4497</v>
       </c>
       <c r="G3" t="n">
         <v>0.1749</v>
@@ -688,13 +688,13 @@
         <v>2.2644</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9816</v>
+        <v>1.1585</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0574</v>
+        <v>0.5518</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9242</v>
+        <v>0.6068</v>
       </c>
       <c r="V3" t="n">
         <v>1.8488</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8954</v>
+        <v>0.4322</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3112</v>
+        <v>1.9803</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4158</v>
+        <v>-1.5481</v>
       </c>
       <c r="G4" t="n">
         <v>1.4819</v>
@@ -766,13 +766,13 @@
         <v>0.9435</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0171</v>
+        <v>-0.4462</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1793</v>
+        <v>-0.1517</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1622</v>
+        <v>-0.2945</v>
       </c>
       <c r="V4" t="n">
         <v>-1.547</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0348</v>
+        <v>-0.8643</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.696</v>
+        <v>-0.5784</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3388</v>
+        <v>-0.2859</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0824</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0476</v>
+        <v>0.2181</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0465</v>
+        <v>0.0711</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0941</v>
+        <v>0.147</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1832</v>
+        <v>-0.8683</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4277</v>
+        <v>-0.269</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2549</v>
@@ -922,13 +922,13 @@
         <v>0.3774</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3057</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2105</v>
+        <v>-0.0543</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.0635</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7832</v>
+        <v>-1.0285</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3994</v>
+        <v>0.3817</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3838</v>
+        <v>-1.4102</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3484</v>
@@ -1000,13 +1000,13 @@
         <v>1.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2651</v>
+        <v>0.4895</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8571</v>
+        <v>-0.076</v>
       </c>
       <c r="U7" t="n">
-        <v>0.592</v>
+        <v>0.5656</v>
       </c>
       <c r="V7" t="n">
         <v>-1.547</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. CAMARA</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8402</v>
+        <v>-3.0293</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6706</v>
+        <v>-2.4902</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1696</v>
+        <v>-0.5391</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.9889</v>
+        <v>-4.6779</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7726</v>
+        <v>-1.7812</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2163</v>
+        <v>-2.8967</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5196</v>
+        <v>-2.3384</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6018</v>
+        <v>-1.1301</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0823</v>
+        <v>-1.2083</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4693</v>
+        <v>-2.3394</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1708</v>
+        <v>-0.6511</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2986</v>
+        <v>-1.6883</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9435</v>
+        <v>0.3774</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9435</v>
+        <v>2.2644</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0922</v>
+        <v>0.9504</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7359</v>
+        <v>0.4901</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3563</v>
+        <v>0.4603</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>O. CAMARA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.547</v>
+        <v>-3.3748</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8227</v>
+        <v>-2.0201</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-1.3547</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.6779</v>
+        <v>-2.9889</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7812</v>
+        <v>-1.7726</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.8967</v>
+        <v>-1.2163</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.3384</v>
+        <v>-0.5196</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1301</v>
+        <v>-0.6018</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2083</v>
+        <v>0.0823</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3394</v>
+        <v>-2.4693</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6511</v>
+        <v>-1.1708</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6883</v>
+        <v>-1.2986</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3774</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.887</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2644</v>
+        <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4326</v>
+        <v>0.5576</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1575</v>
+        <v>0.3865</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2751</v>
+        <v>0.1711</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.784</v>
+        <v>-3.895</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7557</v>
+        <v>-2.627</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0283</v>
+        <v>-1.2679</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.7864</v>
+        <v>-3.1562</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6339</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.1525</v>
+        <v>-3.2408</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0115</v>
+        <v>0.4559</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5869</v>
+        <v>0.8827</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5984</v>
+        <v>-0.4269</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.7749</v>
+        <v>-3.6121</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2208</v>
+        <v>-0.7982</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.5541</v>
+        <v>-2.8139</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1887</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6983</v>
+        <v>2.4531</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8089</v>
+        <v>-0.0595</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8571</v>
+        <v>-0.2524</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0483</v>
+        <v>0.1929</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9024</v>
+        <v>-4.0083</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2906</v>
+        <v>-2.1123</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6118</v>
+        <v>-1.896</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.1562</v>
+        <v>-3.7864</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08450000000000001</v>
+        <v>-0.6339</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.2408</v>
+        <v>-3.1525</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4559</v>
+        <v>-0.0115</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8827</v>
+        <v>0.5869</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4269</v>
+        <v>-0.5984</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.6121</v>
+        <v>-3.7749</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7982</v>
+        <v>-1.2208</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.8139</v>
+        <v>-2.5541</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3774</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8305</v>
+        <v>-1.887</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4531</v>
+        <v>1.6983</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.067</v>
+        <v>-0.0332</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9159</v>
+        <v>-0.2137</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.151</v>
+        <v>0.1805</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.5061</v>
+        <v>-11.0364</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.123600000000001</v>
+        <v>-1.653999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.382400000000001</v>
+        <v>-9.382300000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-13.5302</v>
@@ -1375,13 +1375,13 @@
         <v>-21.6099</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.6754</v>
+        <v>-6.675400000000002</v>
       </c>
       <c r="O12" t="n">
         <v>-14.9346</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.551115123125783e-17</v>
+        <v>-8.326672684688674e-17</v>
       </c>
       <c r="Q12" t="n">
         <v>-14.1525</v>
@@ -1390,10 +1390,10 @@
         <v>14.1525</v>
       </c>
       <c r="S12" t="n">
-        <v>1.948600000000001</v>
+        <v>3.418400000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7293999999999999</v>
+        <v>0.7403</v>
       </c>
       <c r="U12" t="n">
         <v>2.6782</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.1041</v>
+        <v>7.9834</v>
       </c>
       <c r="E13" t="n">
-        <v>7.4556</v>
+        <v>7.9428</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3515</v>
+        <v>0.0406</v>
       </c>
       <c r="G13" t="n">
         <v>6.8396</v>
@@ -1468,13 +1468,13 @@
         <v>1.6983</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2451</v>
+        <v>-0.3658</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9994</v>
+        <v>-0.5122</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2457</v>
+        <v>0.1464</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.489</v>
+        <v>4.7493</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5557</v>
+        <v>3.8737</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9333</v>
+        <v>0.8756</v>
       </c>
       <c r="G14" t="n">
         <v>3.4425</v>
@@ -1546,13 +1546,13 @@
         <v>2.0757</v>
       </c>
       <c r="S14" t="n">
-        <v>1.462</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7141</v>
+        <v>0.0321</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7478</v>
+        <v>0.6902</v>
       </c>
       <c r="V14" t="n">
         <v>1.528</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9675</v>
+        <v>4.4394</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6266</v>
+        <v>2.9445</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3409</v>
+        <v>1.4949</v>
       </c>
       <c r="G15" t="n">
         <v>1.9646</v>
@@ -1624,13 +1624,13 @@
         <v>0.7548</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0029</v>
+        <v>0.4748</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5349</v>
+        <v>-0.1472</v>
       </c>
       <c r="U15" t="n">
-        <v>0.468</v>
+        <v>0.622</v>
       </c>
       <c r="V15" t="n">
         <v>1.2452</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9454</v>
+        <v>2.7393</v>
       </c>
       <c r="E16" t="n">
-        <v>0.008</v>
+        <v>0.5926</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9374</v>
+        <v>2.1467</v>
       </c>
       <c r="G16" t="n">
         <v>1.14</v>
@@ -1702,13 +1702,13 @@
         <v>1.3209</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1946</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5291</v>
+        <v>0.0555</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3345</v>
+        <v>0.5438</v>
       </c>
       <c r="V16" t="n">
         <v>0.6226</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. SANTAMATILDE PERIS</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0473</v>
+        <v>1.2045</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5028</v>
+        <v>0.0386</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5444</v>
+        <v>1.1659</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0361</v>
+        <v>0.5628</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0117</v>
+        <v>0.4414</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0478</v>
+        <v>0.1214</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6792</v>
+        <v>0.249</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0211</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6581</v>
+        <v>0.1645</v>
       </c>
       <c r="M18" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="N18" t="n">
         <v>0.3569</v>
       </c>
-      <c r="N18" t="n">
-        <v>-0.0329</v>
-      </c>
       <c r="O18" t="n">
-        <v>0.3897</v>
+        <v>-0.0431</v>
       </c>
       <c r="P18" t="n">
+        <v>0.7548</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.1887</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="S18" t="n">
         <v>0.1887</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.1887</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-0.1775</v>
-      </c>
       <c r="T18" t="n">
-        <v>-0.1764</v>
+        <v>-0.0218</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0012</v>
+        <v>0.2105</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>V. SANTAMATILDE PERIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.9944</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3512</v>
+        <v>0.5028</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9061</v>
+        <v>0.4915</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5628</v>
+        <v>1.0361</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4414</v>
+        <v>-0.0117</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1214</v>
+        <v>1.0478</v>
       </c>
       <c r="J19" t="n">
-        <v>0.249</v>
+        <v>0.6792</v>
       </c>
       <c r="K19" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0211</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1645</v>
+        <v>0.6581</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3137</v>
+        <v>0.3569</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3569</v>
+        <v>-0.0329</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0431</v>
+        <v>0.3897</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7548</v>
+        <v>0.1887</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9435</v>
+        <v>0.1887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4609</v>
+        <v>-0.2304</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4115</v>
+        <v>-0.1764</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0493</v>
+        <v>-0.0541</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. FONT FENOLLAR</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.41</v>
+        <v>0.5885</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5375</v>
+        <v>-0.2961</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1275</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7521</v>
+        <v>-0.0163</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3623</v>
+        <v>-1.4494</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3897</v>
+        <v>1.433</v>
       </c>
       <c r="J20" t="n">
-        <v>0.655</v>
+        <v>-0.4972</v>
       </c>
       <c r="K20" t="n">
-        <v>0.655</v>
+        <v>-1.1723</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.6751</v>
       </c>
       <c r="M20" t="n">
-        <v>0.097</v>
+        <v>0.4809</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2927</v>
+        <v>-0.277</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3897</v>
+        <v>0.7579</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3421</v>
+        <v>0.416</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1176</v>
+        <v>-0.1007</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2246</v>
+        <v>0.5168</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9434</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MARTÍNEZ JURADO</t>
+          <t>G. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.317</v>
+        <v>0.4629</v>
       </c>
       <c r="E21" t="n">
-        <v>0.317</v>
+        <v>0.5375</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0.0746</v>
       </c>
       <c r="G21" t="n">
-        <v>0.317</v>
+        <v>0.7521</v>
       </c>
       <c r="H21" t="n">
-        <v>0.317</v>
+        <v>0.3623</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.3897</v>
       </c>
       <c r="J21" t="n">
-        <v>0.317</v>
+        <v>0.655</v>
       </c>
       <c r="K21" t="n">
-        <v>0.317</v>
+        <v>0.655</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.2927</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.3897</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-0.2892</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.1176</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-0.1716</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. CERVANTES GUERRA</t>
+          <t>D. MARTÍNEZ JURADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2668</v>
+        <v>0.317</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2735</v>
+        <v>0.317</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0067</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3381</v>
+        <v>0.317</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7333</v>
+        <v>0.317</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0714</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.317</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.317</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2057</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2942</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0172</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.277</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4191</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5879</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1687</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>L. CERVANTES GUERRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3942</v>
+        <v>0.2877</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7833</v>
+        <v>0.0188</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3891</v>
+        <v>0.2689</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0163</v>
+        <v>-0.3381</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4494</v>
+        <v>0.7333</v>
       </c>
       <c r="I23" t="n">
-        <v>1.433</v>
+        <v>-1.0714</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4972</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1723</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6751</v>
+        <v>0.2057</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4809</v>
+        <v>-1.2942</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.277</v>
+        <v>-0.0172</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7579</v>
+        <v>-1.277</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1322</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R23" t="n">
         <v>1.1322</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5667</v>
+        <v>0.1354</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5879</v>
+        <v>-0.2956</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0212</v>
+        <v>0.4309</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9434</v>
+        <v>1.2452</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3691</v>
+        <v>-1.2439</v>
       </c>
       <c r="E24" t="n">
         <v>-1.0765</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2925</v>
+        <v>-0.1673</v>
       </c>
       <c r="G24" t="n">
         <v>1.2929</v>
@@ -2326,13 +2326,13 @@
         <v>1.887</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2845</v>
+        <v>-0.1593</v>
       </c>
       <c r="T24" t="n">
         <v>-0.585</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3005</v>
+        <v>0.4257</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3018</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.6883</v>
+        <v>-2.2962</v>
       </c>
       <c r="E25" t="n">
         <v>-1.9399</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7484</v>
+        <v>-0.3563</v>
       </c>
       <c r="G25" t="n">
         <v>-1.1241</v>
@@ -2404,13 +2404,13 @@
         <v>1.3209</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.338</v>
+        <v>-0.9459</v>
       </c>
       <c r="T25" t="n">
         <v>-0.9406</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3974</v>
+        <v>-0.0053</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6036</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.8445</v>
+        <v>-6.3558</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.4302</v>
+        <v>-5.3071</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.4143</v>
+        <v>-1.0487</v>
       </c>
       <c r="G26" t="n">
         <v>-3.5725</v>
@@ -2482,13 +2482,13 @@
         <v>1.6983</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6149</v>
+        <v>0.1036</v>
       </c>
       <c r="T26" t="n">
-        <v>1.0081</v>
+        <v>0.1312</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3932</v>
+        <v>-0.0276</v>
       </c>
       <c r="V26" t="n">
         <v>-1.566</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>12.5062</v>
+        <v>15.1044</v>
       </c>
       <c r="E27" t="n">
-        <v>9.382499999999997</v>
+        <v>9.3826</v>
       </c>
       <c r="F27" t="n">
-        <v>3.1237</v>
+        <v>5.7218</v>
       </c>
       <c r="G27" t="n">
         <v>13.5305</v>
@@ -2536,7 +2536,7 @@
         <v>21.6099</v>
       </c>
       <c r="K27" t="n">
-        <v>6.675400000000001</v>
+        <v>6.6754</v>
       </c>
       <c r="L27" t="n">
         <v>14.9347</v>
@@ -2551,7 +2551,7 @@
         <v>-0.7547999999999997</v>
       </c>
       <c r="P27" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>6.661338147750939e-16</v>
       </c>
       <c r="Q27" t="n">
         <v>-14.1525</v>
@@ -2560,16 +2560,16 @@
         <v>14.1525</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.9487</v>
+        <v>0.6494999999999999</v>
       </c>
       <c r="T27" t="n">
         <v>-2.6783</v>
       </c>
       <c r="U27" t="n">
-        <v>0.7293000000000003</v>
+        <v>3.327699999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9243999999999997</v>
+        <v>0.9244000000000001</v>
       </c>
       <c r="W27" t="n">
         <v>4.603</v>
